--- a/data/2026-02/reporte_2026-02-23.xlsx
+++ b/data/2026-02/reporte_2026-02-23.xlsx
@@ -640,21 +640,9 @@
           <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ELEVAR SRL</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>30-71439091-7</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>$1.164.000,00</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>DIRECCIÓN REGIONAL ADUANERA CENTRAL</t>
@@ -791,11 +779,7 @@
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>30-70876378-7</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
@@ -891,7 +875,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>texto_completo</t>
+          <t>texto_muestra</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -936,8 +920,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Volver Contrataciones Tercera sección Tercera Preadjudicaciones Detalle | | Ver páginas publicadas Ver texto del aviso MINISTERIO PÚBLICO DE LA DEFENSA - 
-DEFENSORÍA GENERAL DE LA NACIÓN Licitación Pública 49/2025 EXPEDIENTE Nº: 64251/2025 OBJETO: Adquisición de insumos para impresoras OKI instaladas en dependencias del Ministerio Público de la Defensa. LUGAR Y HORARIO DE CONSULTA DEL EXPEDIENTE: Departamento de Compras y Contrataciones - de lunes a viernes de 9.30 a 16:00 hs. – Tacuarí 139/47 P</t>
+          <t>BOLETIN OFICIAL REPUBLICA ARGENTINA Toggle navigation Boletín Oficial de la República Argentina Institucional Productos y servicios Preguntas Frecuentes Contacto × La url ingresada no existe. × Hubo un error en el sistema. Por favor contactarse con el administrador del mismo. × Institucional Misión,</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -982,8 +965,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Volver Contrataciones Tercera sección Tercera Preadjudicaciones Detalle | | Ver páginas publicadas Ver texto del aviso MINISTERIO PÚBLICO DE LA DEFENSA - 
-DEFENSORÍA GENERAL DE LA NACIÓN Licitación Pública 59/2025 EXPEDIENTE: EX-2025-64092- -MPD-DGAD#MPD OBJETO: Adquisición de elementos de seguridad e higiene para dependencias varias del Ministerio Público de la Defensa. LUGAR Y HORARIO DE CONSULTA DEL EXPEDIENTE: Departamento de Compras y Contrataciones- de lunes a viernes de 9.30 a 16:00 hs. –</t>
+          <t>BOLETIN OFICIAL REPUBLICA ARGENTINA Toggle navigation Boletín Oficial de la República Argentina Institucional Productos y servicios Preguntas Frecuentes Contacto × La url ingresada no existe. × Hubo un error en el sistema. Por favor contactarse con el administrador del mismo. × Institucional Misión,</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1028,7 +1010,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Volver Contrataciones Tercera sección Tercera Adjudicaciones Detalle | | Ver páginas publicadas Ver texto del aviso EMPRESA ARGENTINA DE NAVEGACIÓN AÉREA S.E. Licitación Pública (Modo IV) 10/2025 SOLPED N° 10.000.071. “Mantenimiento Correctivo en el Edificio Operativo, Torre de Control, Planta Transmisora, Edificio Radar y Plan de Vuelo en el Aeropuerto de Córdoba” En cumplimiento del Reglamento de Compras y Contrataciones de EANA y de acuerdo al punto xvi) del Artículo XII, se publica el result</t>
+          <t>BOLETIN OFICIAL REPUBLICA ARGENTINA Toggle navigation Boletín Oficial de la República Argentina Institucional Productos y servicios Preguntas Frecuentes Contacto × La url ingresada no existe. × Hubo un error en el sistema. Por favor contactarse con el administrador del mismo. × Institucional Misión,</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1068,25 +1050,12 @@
           <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407959/20260223</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ELEVAR SRL</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>30-71439091-7</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>$1.164.000,00</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Volver Contrataciones Tercera sección Tercera Adjudicaciones Detalle | | Ver páginas publicadas Ver texto del aviso AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - 
-DIRECCIÓN REGIONAL ADUANERA CENTRAL Contratación Directa 01/26 Expediente Nº: EX-2026-00012912- -ARCA-SECFDVAFCE#SDGOAI Objeto de la contratación: Servicio de mantenimiento Ascensor Edificio Sede Aduana Córdoba Adjudicatario ELEVAR SRL CUIT N.º 30-71439091-7 Total Adjudicado: $ 1.164.000,00 La Dirección Regional Aduanera Central informa </t>
+          <t>BOLETIN OFICIAL REPUBLICA ARGENTINA Toggle navigation Boletín Oficial de la República Argentina Institucional Productos y servicios Preguntas Frecuentes Contacto × La url ingresada no existe. × Hubo un error en el sistema. Por favor contactarse con el administrador del mismo. × Institucional Misión,</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1100,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Volver Contrataciones Tercera sección Tercera Adjudicaciones Detalle | | Ver páginas publicadas Ver texto del aviso ARMADA ARGENTINA Licitación Pública 431/2025 UOC: 38/5 - División de Compras - Arsenal Aereonaval Comandante Espora Ejercicio: 2025 Clase: Única Nacional Modalidad: Orden de compra abierta Expediente N°: EX-2025-115587397- -APN-DAA#ARA Objeto: Necesarios contar con dichos repuestos para poner en servicio Aeronave AS555, al que se aplicará este Pliego de Bases y Condiciones Particul</t>
+          <t>BOLETIN OFICIAL REPUBLICA ARGENTINA Toggle navigation Boletín Oficial de la República Argentina Institucional Productos y servicios Preguntas Frecuentes Contacto × La url ingresada no existe. × Hubo un error en el sistema. Por favor contactarse con el administrador del mismo. × Institucional Misión,</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1176,7 +1145,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Volver Contrataciones Tercera sección Tercera Adjudicaciones Detalle | | Ver páginas publicadas Ver texto del aviso ADMINISTRACIÓN NACIONAL DE LA SEGURIDAD SOCIAL Licitación Pública PROCESO COMPR.AR 63-0029-LPU25 PROCESO COMPR.AR N° 63-0029-LPU25 Clase/Causal del procedimiento: Etapa Única Nacional Modalidad: SIN MODALIDAD N° de Expediente Electrónico: EX-2025-54939691- -ANSES-DC#ANSES Objeto: Servicio de control de plagas y un servicio de limpieza de tanques de agua con su análisis físico-quími</t>
+          <t>BOLETIN OFICIAL REPUBLICA ARGENTINA Toggle navigation Boletín Oficial de la República Argentina Institucional Productos y servicios Preguntas Frecuentes Contacto × La url ingresada no existe. × Hubo un error en el sistema. Por favor contactarse con el administrador del mismo. × Institucional Misión,</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1217,15 +1186,11 @@
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>30-70876378-7</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Volver Contrataciones Tercera sección Tercera Adjudicaciones Detalle | | Ver páginas publicadas Ver texto del aviso ADMINISTRACIÓN NACIONAL DE LA SEGURIDAD SOCIAL Licitación Pública PROCESO COMPRAR 63-0063-LPU25 Clase/Causal del procedimiento: Etapa Única Nacional Modalidad: Sin modalidad. Nº de Expediente: EX-2025-85188315-ANSES-DC#ANSES Objeto: Suministro y distribución de bidones de agua potable con provisión e instalación de dispensadores de agua frío/calor compatible, en comodato, incluido </t>
+          <t>BOLETIN OFICIAL REPUBLICA ARGENTINA Toggle navigation Boletín Oficial de la República Argentina Institucional Productos y servicios Preguntas Frecuentes Contacto × La url ingresada no existe. × Hubo un error en el sistema. Por favor contactarse con el administrador del mismo. × Institucional Misión,</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2714,12 +2679,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>38/1-0539-LPU25</t>
+          <t>487-0101-LPU25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Prestación del servicio de preparación de superficie mediante método de arenado y pintado.</t>
+          <t>Servicio para la recepción, elaboración y distribución de alimentos.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2729,7 +2694,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23/02/2026 09:30 Hrs.</t>
+          <t>23/02/2026 10:00 Hrs.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2739,7 +2704,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
+          <t>487 - División Compras y Suministros - Superintendencia de Bienestar de la Policia Federal Argentina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2761,12 +2726,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>487-0101-LPU25</t>
+          <t>38/15-0012-LPU26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Servicio para la recepción, elaboración y distribución de alimentos.</t>
+          <t>Servicio de locación, mantenimiento y gestión de impresiones digitales (Impresión y Fotocopiado)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2786,7 +2751,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>487 - División Compras y Suministros - Superintendencia de Bienestar de la Policia Federal Argentina</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2808,17 +2773,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38/15-0012-LPU26</t>
+          <t>40/47-0629-LPR25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Servicio de locación, mantenimiento y gestión de impresiones digitales (Impresión y Fotocopiado)</t>
+          <t>Servicio de Fotocopiadora para la ESCUELA DE AVAICION MILITAR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2833,7 +2798,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>Departamento Contrataciones Córdoba - UOC 40/47</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2855,12 +2820,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>40/47-0629-LPR25</t>
+          <t>38/18-0063-LPR26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Servicio de Fotocopiadora para la ESCUELA DE AVAICION MILITAR</t>
+          <t>PROVISIÓN DE CARTAS ELECTRÓNICAS PERTENECIENTES AL BUQUE ESCUELA FRAGATA A.R.A. "LIBERTAD".</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2880,7 +2845,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Departamento Contrataciones Córdoba - UOC 40/47</t>
+          <t>38/18 - Division Contrataciones - Comando de Transportes Navales</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2902,12 +2867,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>38/18-0063-LPR26</t>
+          <t>38/18-0057-LPR26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PROVISIÓN DE CARTAS ELECTRÓNICAS PERTENECIENTES AL BUQUE ESCUELA FRAGATA A.R.A. "LIBERTAD".</t>
+          <t>MANTENIMIENTO DE CAMARAS Y COMPRESORES DE FRIGORIFICA PARA EL BUQUE ESCUELA A.R.A. "LIBERTAD"</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2949,17 +2914,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38/18-0057-LPR26</t>
+          <t>37/20-0939-CDI25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE CAMARAS Y COMPRESORES DE FRIGORIFICA PARA EL BUQUE ESCUELA A.R.A. "LIBERTAD"</t>
+          <t>ALQUILER DE DISPENSERS DE AGUA FRIO/CALOR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Contratación Directa</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2974,7 +2939,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>38/18 - Division Contrataciones - Comando de Transportes Navales</t>
+          <t>37/020 - Escuadrón 4 "Concordia"</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2996,17 +2961,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>37/20-0939-CDI25</t>
+          <t>40/51-0023-LPR26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ALQUILER DE DISPENSERS DE AGUA FRIO/CALOR</t>
+          <t>Adquisición de Medicamentos Analgésicos, Antiinflamatorios, Psicotrópicos, Y Otros Para El HACBA.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3021,7 +2986,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>37/020 - Escuadrón 4 "Concordia"</t>
+          <t>Departamento Contrataciones Córdoba - UOC 40/51</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3043,12 +3008,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>40/51-0023-LPR26</t>
+          <t>84/19-0091-LPR26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Adquisición de Medicamentos Analgésicos, Antiinflamatorios, Psicotrópicos, Y Otros Para El HACBA.</t>
+          <t>ADQUISICIÓN DE MATERIALES DE FERRETERIA Y ELECTRICIDAD PARA EL CDO BR M VIII Y UU - 2DO TRIM 2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3068,7 +3033,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Departamento Contrataciones Córdoba - UOC 40/51</t>
+          <t>84/19 - Comando Brigada de Montaña VIII</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3090,22 +3055,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>84/19-0091-LPR26</t>
+          <t>40/23-0984-CDI25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE MATERIALES DE FERRETERIA Y ELECTRICIDAD PARA EL CDO BR M VIII Y UU - 2DO TRIM 2026</t>
+          <t>SERVICIO DE FUMIGACION</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Contratación Directa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23/02/2026 10:00 Hrs.</t>
+          <t>23/02/2026 10:30 Hrs.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3115,7 +3080,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>84/19 - Comando Brigada de Montaña VIII</t>
+          <t>40/023 - DIVISIÓN CONTRATACIONES MORENO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3137,22 +3102,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>40/23-0984-CDI25</t>
+          <t>84/71-0006-LPR26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SERVICIO DE FUMIGACION</t>
+          <t>SERVICIO DE TRANSPORTE DEL PERSONAL DEL INSTITUTO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>23/02/2026 10:30 Hrs.</t>
+          <t>23/02/2026 12:00 Hrs.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3162,7 +3127,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>40/023 - DIVISIÓN CONTRATACIONES MORENO</t>
+          <t>84/71 - Liceo Militar General Roca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/data/2026-02/reporte_2026-02-23.xlsx
+++ b/data/2026-02/reporte_2026-02-23.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🚨 Cruce" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🚨 Flujo Completo" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🏆 Adjudicaciones" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📰 BORA Licitaciones" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🛒 Comprar" sheetId="4" state="visible" r:id="rId4"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,29 +432,29 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>tipo_proceso_bora</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>link_bora</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>proveedor_adjudicado</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>cuit_proveedor</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>monto_adjudicado_bora</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>tipo_proceso</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>link_bora</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
           <t>en_comprar</t>
@@ -472,20 +472,30 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>en_tgn</t>
+          <t>nro_proceso_comprar</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>cobro_en_tgn</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>beneficiario_tgn</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>monto_pagado_tgn</t>
-        </is>
-      </c>
       <c r="N1" t="inlineStr">
+        <is>
+          <t>monto_cobrado_tgn</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>etapa</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>alerta</t>
         </is>
@@ -502,19 +512,19 @@
           <t>MINISTERIO PÚBLICO DE LA DEFENSA -</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DEFENSORÍA GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407956/20260223</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>DEFENSORÍA GENERAL DE LA NACIÓN</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407956/20260223</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>❌ NO</t>
@@ -524,14 +534,20 @@
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
         <is>
           <t>❌ NO</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>📋 SOLO BORA</t>
         </is>
@@ -548,19 +564,19 @@
           <t>MINISTERIO PÚBLICO DE LA DEFENSA -</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DEFENSORÍA GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407957/20260223</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>DEFENSORÍA GENERAL DE LA NACIÓN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407957/20260223</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>❌ NO</t>
@@ -570,14 +586,20 @@
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>❌ NO</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>📋 SOLO BORA</t>
         </is>
@@ -594,19 +616,19 @@
           <t>EMPRESA ARGENTINA DE NAVEGACIÓN AÉREA S.E.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Licitación Pública (Modo IV) 10/2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407958/20260223</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Licitación Pública (Modo IV) 10/2025</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407958/20260223</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>❌ NO</t>
@@ -616,14 +638,20 @@
         <v>0</v>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>❌ NO</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>📋 SOLO BORA</t>
         </is>
@@ -640,17 +668,25 @@
           <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>DIRECCIÓN REGIONAL ADUANERA CENTRAL</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407959/20260223</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ELEVAR SRL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407959/20260223</t>
+          <t>$1.164.000,00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -662,14 +698,20 @@
         <v>0</v>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>❌ NO</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>📋 SOLO BORA</t>
         </is>
@@ -686,19 +728,19 @@
           <t>ARMADA ARGENTINA</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Licitación Pública 431/2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407960/20260223</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Licitación Pública 431/2025</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407960/20260223</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>❌ NO</t>
@@ -708,14 +750,20 @@
         <v>0</v>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>❌ NO</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>📋 SOLO BORA</t>
         </is>
@@ -732,19 +780,19 @@
           <t>ADMINISTRACIÓN NACIONAL DE LA SEGURIDAD SOCIAL</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Licitación Pública PROCESO COMPR.AR 63-0029-LPU25</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407961/20260223</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Licitación Pública PROCESO COMPR.AR 63-0029-LPU25</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407961/20260223</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>❌ NO</t>
@@ -754,14 +802,20 @@
         <v>0</v>
       </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>❌ NO</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>📋 SOLO BORA</t>
         </is>
@@ -778,19 +832,23 @@
           <t>ADMINISTRACIÓN NACIONAL DE LA SEGURIDAD SOCIAL</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Licitación Pública PROCESO COMPRAR  63-0063-LPU25</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407962/20260223</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Licitación Pública PROCESO COMPRAR  63-0063-LPU25</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407962/20260223</t>
-        </is>
-      </c>
+          <t>33-57391612-9</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>❌ NO</t>
@@ -800,14 +858,20 @@
         <v>0</v>
       </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>❌ NO</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>📋 SOLO BORA</t>
         </is>
@@ -920,7 +984,12 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>BOLETIN OFICIAL REPUBLICA ARGENTINA Toggle navigation Boletín Oficial de la República Argentina Institucional Productos y servicios Preguntas Frecuentes Contacto × La url ingresada no existe. × Hubo un error en el sistema. Por favor contactarse con el administrador del mismo. × Institucional Misión,</t>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/M1BQM25YUzFMUVpSbkVWUVVZR3c4dz09
+MINISTERIO PÚBLICO DE LA DEFENSA - DEFENSORÍA GENERAL
+DE LA NACIÓN
+Licitación Pública 49/2025
+EXPEDIENTE Nº: 64251/2025 OBJETO: Adquisición de insumos para impresoras OKI instaladas en
+dependencias  del  Ministerio  Púb</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -965,7 +1034,12 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>BOLETIN OFICIAL REPUBLICA ARGENTINA Toggle navigation Boletín Oficial de la República Argentina Institucional Productos y servicios Preguntas Frecuentes Contacto × La url ingresada no existe. × Hubo un error en el sistema. Por favor contactarse con el administrador del mismo. × Institucional Misión,</t>
+          <t xml:space="preserve">MINISTERIO PÚBLICO DE LA DEFENSA - DEFENSORÍA GENERAL
+DE LA NACIÓN
+https://www.boletinoficial.gob.ar/pdf/linkQR/MHcvWlcwelBxQUJSbkVWUVVZR3c4dz09
+Licitación Pública 59/2025
+EXPEDIENTE: EX-2025-64092- -MPD-DGAD#MPD OBJETO: Adquisición de elementos de seguridad e
+higiene  para  dependencias  varias </t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1010,7 +1084,11 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>BOLETIN OFICIAL REPUBLICA ARGENTINA Toggle navigation Boletín Oficial de la República Argentina Institucional Productos y servicios Preguntas Frecuentes Contacto × La url ingresada no existe. × Hubo un error en el sistema. Por favor contactarse con el administrador del mismo. × Institucional Misión,</t>
+          <t xml:space="preserve">https://www.boletinoficial.gob.ar/pdf/linkQR/VlhjMkNVL0VDcVpSbkVWUVVZR3c4dz09
+EMPRESA ARGENTINA DE NAVEGACIÓN AÉREA S.E.
+Licitación Pública (Modo IV) 10/2025
+SOLPED N° 10.000.071. “Mantenimiento Correctivo en el Edificio Operativo, Torre de Control, Planta
+Transmisora,  Edificio  Radar  y  Plan  </t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1050,12 +1128,25 @@
           <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407959/20260223</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ELEVAR SRL</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>$1.164.000,00</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>BOLETIN OFICIAL REPUBLICA ARGENTINA Toggle navigation Boletín Oficial de la República Argentina Institucional Productos y servicios Preguntas Frecuentes Contacto × La url ingresada no existe. × Hubo un error en el sistema. Por favor contactarse con el administrador del mismo. × Institucional Misión,</t>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/c0tmVklObXQ4T3BSbkVWUVVZR3c4dz09
+AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -
+DIRECCIÓN REGIONAL ADUANERA CENTRAL
+Contratación Directa 01/26
+Expediente Nº: EX-2026-00012912- -ARCA-SECFDVAFCE#SDGOAI Objeto de la contratación: Servicio
+de mantenimiento As</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1100,7 +1191,11 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>BOLETIN OFICIAL REPUBLICA ARGENTINA Toggle navigation Boletín Oficial de la República Argentina Institucional Productos y servicios Preguntas Frecuentes Contacto × La url ingresada no existe. × Hubo un error en el sistema. Por favor contactarse con el administrador del mismo. × Institucional Misión,</t>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/dlVNb21uUVFoUWRSbkVWUVVZR3c4dz09
+ARMADA ARGENTINA
+Licitación Pública 431/2025
+UOC: 38/5 - División de Compras - Arsenal Aereonaval Comandante Espora Ejercicio: 2025 Clase: Única
+Nacional Modalidad: Orden de compra abierta Expediente N°: EX-2025-1155873</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1145,7 +1240,11 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>BOLETIN OFICIAL REPUBLICA ARGENTINA Toggle navigation Boletín Oficial de la República Argentina Institucional Productos y servicios Preguntas Frecuentes Contacto × La url ingresada no existe. × Hubo un error en el sistema. Por favor contactarse con el administrador del mismo. × Institucional Misión,</t>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/SGlvRG5lUlFnd3RSbkVWUVVZR3c4dz09
+ADMINISTRACIÓN NACIONAL DE LA SEGURIDAD SOCIAL
+Licitación Pública PROCESO COMPR.AR 63-0029-LPU25
+PROCESO COMPR.AR N° 63-0029-LPU25 Clase/Causal del procedimiento: Etapa Única Nacional
+Modalidad: SIN MODALIDAD N° de Expe</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1186,11 +1285,19 @@
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>33-57391612-9</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>BOLETIN OFICIAL REPUBLICA ARGENTINA Toggle navigation Boletín Oficial de la República Argentina Institucional Productos y servicios Preguntas Frecuentes Contacto × La url ingresada no existe. × Hubo un error en el sistema. Por favor contactarse con el administrador del mismo. × Institucional Misión,</t>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/ZzhIeEJJMmZLTU5SbkVWUVVZR3c4dz09
+ADMINISTRACIÓN NACIONAL DE LA SEGURIDAD SOCIAL
+Licitación Pública PROCESO COMPRAR 63-0063-LPU25
+Clase/Causal del procedimiento: Etapa Única Nacional Modalidad: Sin modalidad. Nº de Expediente: EX-
+2025-85188315-ANSES-DC</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">

--- a/data/2026-02/reporte_2026-02-23.xlsx
+++ b/data/2026-02/reporte_2026-02-23.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🏆 Adjudicaciones" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📰 BORA Licitaciones" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🛒 Comprar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⚠️ Riesgo Licitatorio" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,6 +501,26 @@
           <t>alerta</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>indicadores_riesgo</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>score_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>indice_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>nivel_riesgo_licit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,12 +530,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MINISTERIO PÚBLICO DE LA DEFENSA -</t>
+          <t>MINISTERIO PÚBLICO DE LA DEFENSA - DEFENSORÍA GENERAL DE LA NACIÓN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEFENSORÍA GENERAL DE LA NACIÓN</t>
+          <t>Licitación Pública 49/2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -552,6 +573,22 @@
           <t>📋 SOLO BORA</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>🟡 Adjudicación mismo día de publicación</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -561,12 +598,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MINISTERIO PÚBLICO DE LA DEFENSA -</t>
+          <t>MINISTERIO PÚBLICO DE LA DEFENSA - DEFENSORÍA GENERAL DE LA NACIÓN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEFENSORÍA GENERAL DE LA NACIÓN</t>
+          <t>Licitación Pública 59/2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -604,6 +641,22 @@
           <t>📋 SOLO BORA</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>🟡 Adjudicación mismo día de publicación</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -656,6 +709,22 @@
           <t>📋 SOLO BORA</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>🟡 Adjudicación mismo día de publicación</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -665,12 +734,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -</t>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA CENTRAL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANERA CENTRAL</t>
+          <t>Contratación Directa 01/26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -714,6 +783,22 @@
       <c r="P5" t="inlineStr">
         <is>
           <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>🔴 Contratación Directa | 🟡 Adjudicación mismo día de publicación</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Medio</t>
         </is>
       </c>
     </row>
@@ -768,6 +853,22 @@
           <t>📋 SOLO BORA</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>🟡 Adjudicación mismo día de publicación</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -820,6 +921,22 @@
           <t>📋 SOLO BORA</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>🟡 Adjudicación mismo día de publicación</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -874,6 +991,22 @@
       <c r="P8" t="inlineStr">
         <is>
           <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>🟡 Adjudicación mismo día de publicación</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Bajo</t>
         </is>
       </c>
     </row>
@@ -961,12 +1094,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MINISTERIO PÚBLICO DE LA DEFENSA -</t>
+          <t>MINISTERIO PÚBLICO DE LA DEFENSA - DEFENSORÍA GENERAL DE LA NACIÓN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DEFENSORÍA GENERAL DE LA NACIÓN</t>
+          <t>Licitación Pública 49/2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1011,12 +1144,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MINISTERIO PÚBLICO DE LA DEFENSA -</t>
+          <t>MINISTERIO PÚBLICO DE LA DEFENSA - DEFENSORÍA GENERAL DE LA NACIÓN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DEFENSORÍA GENERAL DE LA NACIÓN</t>
+          <t>Licitación Pública 59/2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1110,12 +1243,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -</t>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA CENTRAL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANERA CENTRAL</t>
+          <t>Contratación Directa 01/26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1740,12 +1873,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -</t>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN DE COMPRAS, INFRAESTRUCTURA Y LOGÍSTICA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE COMPRAS, INFRAESTRUCTURA Y LOGÍSTICA</t>
+          <t>Licitación Pública A0PC000000-0010-LPU25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1785,12 +1918,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -</t>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN DE COMPRAS, INFRAESTRUCTURA Y LOGÍSTICA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE COMPRAS, INFRAESTRUCTURA Y LOGÍSTICA</t>
+          <t>Licitación Pública A0PC000000-0010-LPU25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2100,12 +2233,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -</t>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL MENDOZA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL MENDOZA</t>
+          <t>Licitación Pública 5/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2460,12 +2593,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -</t>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN DE COMPRAS, INFRAESTRUCTURA Y LOGÍSTICA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE COMPRAS, INFRAESTRUCTURA Y LOGÍSTICA</t>
+          <t>Licitación Pública A0PC000000-0008-LPU25</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2640,12 +2773,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -</t>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL JUNÍN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL JUNÍN</t>
+          <t>Licitación Pública 0000003/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2786,22 +2919,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>487-0101-LPU25</t>
+          <t>84/11-2048-LPR25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Servicio para la recepción, elaboración y distribución de alimentos.</t>
+          <t>CONTRATAR UN SERVICIO PARA LA PERFORACIÓN DE POZO DE AGUA.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23/02/2026 10:00 Hrs.</t>
+          <t>24/02/2026 08:00 Hrs.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2811,7 +2944,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>487 - División Compras y Suministros - Superintendencia de Bienestar de la Policia Federal Argentina</t>
+          <t>84/11 - Liceo Militar General San Martin</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2833,22 +2966,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>38/15-0012-LPU26</t>
+          <t>84/11-2119-LPR25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Servicio de locación, mantenimiento y gestión de impresiones digitales (Impresión y Fotocopiado)</t>
+          <t>CONTRATAR UN SERVICIO DE MANTENIMIENTO Y LIMPIEZA DE LA RED CLOACAL Y CÁMARAS SEPTICAS.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23/02/2026 10:00 Hrs.</t>
+          <t>24/02/2026 08:00 Hrs.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2858,7 +2991,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/11 - Liceo Militar General San Martin</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2880,12 +3013,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40/47-0629-LPR25</t>
+          <t>84/71-0038-LPR26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Servicio de Fotocopiadora para la ESCUELA DE AVAICION MILITAR</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE HOSTING WEB ANUAL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2895,7 +3028,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23/02/2026 10:00 Hrs.</t>
+          <t>24/02/2026 08:00 Hrs.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2905,7 +3038,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Departamento Contrataciones Córdoba - UOC 40/47</t>
+          <t>84/71 - Liceo Militar General Roca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2927,22 +3060,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>38/18-0063-LPR26</t>
+          <t>40/16-0062-CDI26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PROVISIÓN DE CARTAS ELECTRÓNICAS PERTENECIENTES AL BUQUE ESCUELA FRAGATA A.R.A. "LIBERTAD".</t>
+          <t>ADQUISICION DE SERVICIO DE RESIDUOS PATOLOGICOS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Contratación Directa</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23/02/2026 10:00 Hrs.</t>
+          <t>24/02/2026 08:00 Hrs.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2952,7 +3085,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>38/18 - Division Contrataciones - Comando de Transportes Navales</t>
+          <t>40/016 - AREA MATERIAL QUILMES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2974,22 +3107,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>38/18-0057-LPR26</t>
+          <t>40/16-0036-CDI26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE CAMARAS Y COMPRESORES DE FRIGORIFICA PARA EL BUQUE ESCUELA A.R.A. "LIBERTAD"</t>
+          <t>ADQUISICION DE MATERIALES ELECTRICOS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Contratación Directa</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23/02/2026 10:00 Hrs.</t>
+          <t>24/02/2026 08:00 Hrs.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2999,7 +3132,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>38/18 - Division Contrataciones - Comando de Transportes Navales</t>
+          <t>40/016 - AREA MATERIAL QUILMES</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3021,22 +3154,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37/20-0939-CDI25</t>
+          <t>40/16-0017-LPR26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ALQUILER DE DISPENSERS DE AGUA FRIO/CALOR</t>
+          <t>ADQUISICIÓN DE INSUMOS CÁRNICOS PAR ELABORACIÓN DE ALIMENTOS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>23/02/2026 10:00 Hrs.</t>
+          <t>24/02/2026 08:00 Hrs.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3046,7 +3179,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>37/020 - Escuadrón 4 "Concordia"</t>
+          <t>40/016 - AREA MATERIAL QUILMES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3068,12 +3201,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>40/51-0023-LPR26</t>
+          <t>74/45-0023-LPR26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Adquisición de Medicamentos Analgésicos, Antiinflamatorios, Psicotrópicos, Y Otros Para El HACBA.</t>
+          <t>ADQUISICION DE HERRAMIENTAS ELECTRICAS MENORES PARA EL PN ISLAS DE SANTA FE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3083,7 +3216,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23/02/2026 10:00 Hrs.</t>
+          <t>24/02/2026 08:00 Hrs.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3093,7 +3226,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Departamento Contrataciones Córdoba - UOC 40/51</t>
+          <t>74/45 - Parque Nacional Islas de Santa Fe</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3115,22 +3248,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>84/19-0091-LPR26</t>
+          <t>39-0004-LPU26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE MATERIALES DE FERRETERIA Y ELECTRICIDAD PARA EL CDO BR M VIII Y UU - 2DO TRIM 2026</t>
+          <t>ADQUISICIÓN E INSTALACIÓN DE CUATRO (4) COMPRESORES DE AIRE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>23/02/2026 10:00 Hrs.</t>
+          <t>24/02/2026 09:00 Hrs.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3140,7 +3273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>84/19 - Comando Brigada de Montaña VIII</t>
+          <t>39 - Dirección General de Administración- PNA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3162,22 +3295,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>40/23-0984-CDI25</t>
+          <t>38/3-1320-LPR25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SERVICIO DE FUMIGACION</t>
+          <t>ADQUISICION DE REPUESTOS PARA MOTOR FUERA DE BORDA (BNPB)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23/02/2026 10:30 Hrs.</t>
+          <t>24/02/2026 09:00 Hrs.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3187,7 +3320,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>40/023 - DIVISIÓN CONTRATACIONES MORENO</t>
+          <t>38/03 - UOC de la Intendencia Naval Puerto Belgrano - Armada Argentina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3209,12 +3342,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>84/71-0006-LPR26</t>
+          <t>38/3-1638-LPR25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRANSPORTE DEL PERSONAL DEL INSTITUTO</t>
+          <t>ADQUISICION DE MATERIALES ELECTRICOS PARA LAS SUBESTACIONES (BNPB)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3224,7 +3357,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>23/02/2026 12:00 Hrs.</t>
+          <t>24/02/2026 09:00 Hrs.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3234,7 +3367,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>84/71 - Liceo Militar General Roca</t>
+          <t>38/03 - UOC de la Intendencia Naval Puerto Belgrano - Armada Argentina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3339,6 +3472,440 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>Comprar.gob.ar</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>organismo_contratante</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tipo_proceso_bora</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado_bora</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>indicadores_riesgo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>score_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>indice_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>nivel_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>etapa</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>link_bora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA CENTRAL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Contratación Directa 01/26</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>$1.164.000,00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>🔴 Contratación Directa | 🟡 Adjudicación mismo día de publicación</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407959/20260223</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MINISTERIO PÚBLICO DE LA DEFENSA - DEFENSORÍA GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Licitación Pública 59/2025</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>🟡 Adjudicación mismo día de publicación</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407957/20260223</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MINISTERIO PÚBLICO DE LA DEFENSA - DEFENSORÍA GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Licitación Pública 49/2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>🟡 Adjudicación mismo día de publicación</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407956/20260223</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EMPRESA ARGENTINA DE NAVEGACIÓN AÉREA S.E.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Licitación Pública (Modo IV) 10/2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>🟡 Adjudicación mismo día de publicación</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407958/20260223</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Licitación Pública 431/2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>🟡 Adjudicación mismo día de publicación</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407960/20260223</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN NACIONAL DE LA SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Licitación Pública PROCESO COMPR.AR 63-0029-LPU25</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>🟡 Adjudicación mismo día de publicación</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407961/20260223</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN NACIONAL DE LA SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Licitación Pública PROCESO COMPRAR  63-0063-LPU25</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>33-57391612-9</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>🟡 Adjudicación mismo día de publicación</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407962/20260223</t>
         </is>
       </c>
     </row>
